--- a/data/resume/toubiao.xlsx
+++ b/data/resume/toubiao.xlsx
@@ -1195,7 +1195,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CAEACE"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
